--- a/results_(stress_test)_PCCxSigmoid-PLI-/cnn_evaluation(stress_test)_k-heaviside_p-40_nm_basis-False_nm_modifier-False.xlsx
+++ b/results_(stress_test)_PCCxSigmoid-PLI-/cnn_evaluation(stress_test)_k-heaviside_p-40_nm_basis-False_nm_modifier-False.xlsx
@@ -10,6 +10,7 @@
     <sheet name="nrr_8" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="summary_t" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="nrr_4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1076,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1139,6 +1140,44 @@
         <v>4.713269447709956</v>
       </c>
       <c r="E3" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>57.03711393120471</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56.36688785634752</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9614718267321585</v>
+      </c>
+      <c r="D4" t="n">
+        <v>57.03711393120471</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.846137932873562</v>
+      </c>
+      <c r="B5" t="n">
+        <v>6.063282134778643</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.1176348156243788</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.846137932873562</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>Std</t>
         </is>
@@ -1155,7 +1194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1226,6 +1265,681 @@
         <v>0.1459258375142329</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>57.03711393120471</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5.846137932873562</v>
+      </c>
+      <c r="C3" t="n">
+        <v>56.36688785634752</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.063282134778643</v>
+      </c>
+      <c r="E3" t="n">
+        <v>57.03711393120471</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5.846137932873562</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9614718267321585</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1176348156243788</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>56.67851798025934</v>
+      </c>
+      <c r="C2" t="n">
+        <v>56.09671698442694</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9960385859012604</v>
+      </c>
+      <c r="E2" t="n">
+        <v>56.67851798025934</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>57.59764357823165</v>
+      </c>
+      <c r="C3" t="n">
+        <v>57.50617982291491</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9152151008447011</v>
+      </c>
+      <c r="E3" t="n">
+        <v>57.59764357823165</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>56.18171437469182</v>
+      </c>
+      <c r="C4" t="n">
+        <v>55.61010726026893</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9935444583495456</v>
+      </c>
+      <c r="E4" t="n">
+        <v>56.18171437469183</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>51.1424839315219</v>
+      </c>
+      <c r="C5" t="n">
+        <v>50.39859847382977</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.030399169027805</v>
+      </c>
+      <c r="E5" t="n">
+        <v>51.1424839315219</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>52.93428143842075</v>
+      </c>
+      <c r="C6" t="n">
+        <v>52.5314300257179</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.015161680181821</v>
+      </c>
+      <c r="E6" t="n">
+        <v>52.93428143842075</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>54.31379164179621</v>
+      </c>
+      <c r="C7" t="n">
+        <v>53.88113664426017</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.9630743871132532</v>
+      </c>
+      <c r="E7" t="n">
+        <v>54.31379164179621</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>63.01741364544675</v>
+      </c>
+      <c r="C8" t="n">
+        <v>61.89097104918164</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7893381382028262</v>
+      </c>
+      <c r="E8" t="n">
+        <v>63.01741364544675</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>60.41964030830717</v>
+      </c>
+      <c r="C9" t="n">
+        <v>59.28342444446029</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8984760850667953</v>
+      </c>
+      <c r="E9" t="n">
+        <v>60.41964030830717</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>59.68338826460437</v>
+      </c>
+      <c r="C10" t="n">
+        <v>59.04841479387905</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9493288973967235</v>
+      </c>
+      <c r="E10" t="n">
+        <v>59.68338826460437</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>53.58515212069309</v>
+      </c>
+      <c r="C11" t="n">
+        <v>52.98896462684273</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.062502725919088</v>
+      </c>
+      <c r="E11" t="n">
+        <v>53.58515212069308</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>52.95858960717653</v>
+      </c>
+      <c r="C12" t="n">
+        <v>52.23590792605034</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.065501985947291</v>
+      </c>
+      <c r="E12" t="n">
+        <v>52.95858960717653</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>58.750854246144</v>
+      </c>
+      <c r="C13" t="n">
+        <v>58.32486302223317</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.9095464209715525</v>
+      </c>
+      <c r="E13" t="n">
+        <v>58.750854246144</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>49.98685109732783</v>
+      </c>
+      <c r="C14" t="n">
+        <v>49.08211758544343</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.044708557923635</v>
+      </c>
+      <c r="E14" t="n">
+        <v>49.98685109732784</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>52.51991799237017</v>
+      </c>
+      <c r="C15" t="n">
+        <v>52.29894415143353</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.061841444174449</v>
+      </c>
+      <c r="E15" t="n">
+        <v>52.51991799237017</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>51.11142829955276</v>
+      </c>
+      <c r="C16" t="n">
+        <v>49.78114359559603</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.108401953180631</v>
+      </c>
+      <c r="E16" t="n">
+        <v>51.11142829955277</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>59.31080718691338</v>
+      </c>
+      <c r="C17" t="n">
+        <v>58.73137288663892</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.9293607652187348</v>
+      </c>
+      <c r="E17" t="n">
+        <v>59.31080718691338</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>55.97920397235271</v>
+      </c>
+      <c r="C18" t="n">
+        <v>55.05481968753256</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.9499162574609121</v>
+      </c>
+      <c r="E18" t="n">
+        <v>55.97920397235271</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>59.61954688189344</v>
+      </c>
+      <c r="C19" t="n">
+        <v>58.58930370352971</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.9029610385497412</v>
+      </c>
+      <c r="E19" t="n">
+        <v>59.61954688189344</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>56.91329509770846</v>
+      </c>
+      <c r="C20" t="n">
+        <v>56.91789513532035</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.9686497221390405</v>
+      </c>
+      <c r="E20" t="n">
+        <v>56.91329509770846</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>52.90236074706529</v>
+      </c>
+      <c r="C21" t="n">
+        <v>50.06516053707664</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.147458528975646</v>
+      </c>
+      <c r="E21" t="n">
+        <v>52.90236074706529</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>60.36358446007318</v>
+      </c>
+      <c r="C22" t="n">
+        <v>59.95034520857438</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.9372020304203034</v>
+      </c>
+      <c r="E22" t="n">
+        <v>60.36358446007318</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>52.70175347537609</v>
+      </c>
+      <c r="C23" t="n">
+        <v>52.12881307716225</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.021224025885264</v>
+      </c>
+      <c r="E23" t="n">
+        <v>52.70175347537609</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>52.57960709002673</v>
+      </c>
+      <c r="C24" t="n">
+        <v>52.2362859847838</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.056726570924123</v>
+      </c>
+      <c r="E24" t="n">
+        <v>52.57960709002673</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>52.07622903312313</v>
+      </c>
+      <c r="C25" t="n">
+        <v>51.05503871654948</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.030511045455933</v>
+      </c>
+      <c r="E25" t="n">
+        <v>52.07622903312313</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>57.68717722471648</v>
+      </c>
+      <c r="C26" t="n">
+        <v>56.78968131035833</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.9703006953001022</v>
+      </c>
+      <c r="E26" t="n">
+        <v>57.68717722471648</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>51.61947767714254</v>
+      </c>
+      <c r="C27" t="n">
+        <v>50.21102693226844</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.072956330577532</v>
+      </c>
+      <c r="E27" t="n">
+        <v>51.61947767714254</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>56.32989904756962</v>
+      </c>
+      <c r="C28" t="n">
+        <v>56.32505584978126</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.955120583375295</v>
+      </c>
+      <c r="E28" t="n">
+        <v>56.32989904756962</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>69.23070268773952</v>
+      </c>
+      <c r="C29" t="n">
+        <v>69.03229265754211</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.6878358249862988</v>
+      </c>
+      <c r="E29" t="n">
+        <v>69.23070268773952</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>65.3403576155503</v>
+      </c>
+      <c r="C30" t="n">
+        <v>65.59504118649542</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.8305335303147633</v>
+      </c>
+      <c r="E30" t="n">
+        <v>65.3403576155503</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>77.57774721234613</v>
+      </c>
+      <c r="C31" t="n">
+        <v>77.36558241027323</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.5803182621796925</v>
+      </c>
+      <c r="E31" t="n">
+        <v>77.57774721234613</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>57.03711393120471</v>
+      </c>
+      <c r="C32" t="n">
+        <v>56.36688785634752</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.9614718267321585</v>
+      </c>
+      <c r="E32" t="n">
+        <v>57.03711393120471</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5.846137932873562</v>
+      </c>
+      <c r="C33" t="n">
+        <v>6.063282134778643</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1176348156243788</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5.846137932873562</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
